--- a/model_documentation/IRS_Valuation_Output_Map.xlsx
+++ b/model_documentation/IRS_Valuation_Output_Map.xlsx
@@ -537,7 +537,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IRS Valuation Output Field Map  —  IRS_Valuation_&lt;val_date&gt;-00001.csv  (49 columns, A–AW)</t>
+          <t>IRS Valuation Output Field Map  —  IRS_Valuation_&lt;val_date&gt;-&lt;NNNNN&gt;.csv  (49 columns, A–AW)</t>
         </is>
       </c>
     </row>
